--- a/dist/data/Base_CeNtro Partner.xlsx
+++ b/dist/data/Base_CeNtro Partner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/GitHub/CeNtro Partner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="492" documentId="13_ncr:1_{760AD2FD-697A-4E92-8D4F-188A5F96FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{116830F0-27A5-4027-8928-ACFFC964DB35}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="13_ncr:1_{760AD2FD-697A-4E92-8D4F-188A5F96FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B41ABCCE-996D-480D-854C-83B4D1492F3E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{38B5B763-1661-4426-8397-08C7B1466D39}"/>
   </bookViews>
@@ -710,7 +710,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -780,47 +780,32 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -898,38 +883,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="6"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1271,7 +1224,227 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1399,102 +1572,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2671,128 +2748,36 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="6"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -2810,7 +2795,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}" name="instrucciones" displayName="instrucciones" ref="A1:E19" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}" name="instrucciones" displayName="instrucciones" ref="A1:E19" totalsRowShown="0" headerRowDxfId="148" tableBorderDxfId="147">
   <autoFilter ref="A1:E19" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E19">
     <sortCondition ref="A2:A19" customList="Partner,Cliente,Negocio"/>
@@ -2827,63 +2812,63 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{8C5E01EB-7341-4843-915C-8257323248EA}" name="Desempeño" displayName="Desempeño" ref="A1:H73" dataDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{8C5E01EB-7341-4843-915C-8257323248EA}" name="Desempeño" displayName="Desempeño" ref="A1:H73" dataDxfId="86">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{78AD0C5E-A8AA-4CB3-9168-E0107531279B}" name="CeCo" dataDxfId="78"/>
-    <tableColumn id="2" xr3:uid="{75AC09E7-B3E2-4E40-8A4C-B26E4D39223A}" name="ene" dataDxfId="77" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{7E78693C-A6A2-4AF3-9193-850E3285B095}" name="feb" dataDxfId="76" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{9B2459EF-EF12-44AE-8E56-7C0B7BFE3858}" name="mar" dataDxfId="75" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{8882EEB9-4FFD-4D23-96E1-073C5DD693F1}" name="abr" dataDxfId="74" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{D5CF8872-BAE8-4C0C-9493-2F30EFA10DBD}" name="may" dataDxfId="73" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{9E15206F-3384-46EB-AD0D-E866369B8131}" name="jun" dataDxfId="72" dataCellStyle="Normal 2"/>
-    <tableColumn id="8" xr3:uid="{2201D65E-28DD-4748-8399-A4DCBFF2D8A0}" name="YTD" dataDxfId="71" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{78AD0C5E-A8AA-4CB3-9168-E0107531279B}" name="CeCo" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{75AC09E7-B3E2-4E40-8A4C-B26E4D39223A}" name="ene" dataDxfId="84" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{7E78693C-A6A2-4AF3-9193-850E3285B095}" name="feb" dataDxfId="83" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{9B2459EF-EF12-44AE-8E56-7C0B7BFE3858}" name="mar" dataDxfId="82" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{8882EEB9-4FFD-4D23-96E1-073C5DD693F1}" name="abr" dataDxfId="81" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{D5CF8872-BAE8-4C0C-9493-2F30EFA10DBD}" name="may" dataDxfId="80" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{9E15206F-3384-46EB-AD0D-E866369B8131}" name="jun" dataDxfId="79" dataCellStyle="Normal 2"/>
+    <tableColumn id="8" xr3:uid="{2201D65E-28DD-4748-8399-A4DCBFF2D8A0}" name="YTD" dataDxfId="78" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1F78B71A-1B12-4FB8-AEC0-1B482898E867}" name="Bebida" displayName="Bebida" ref="A1:H73" dataDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1F78B71A-1B12-4FB8-AEC0-1B482898E867}" name="Bebida" displayName="Bebida" ref="A1:H73" dataDxfId="77">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{AC74C680-FF83-44A5-A570-52AEBB5DE765}" name="CeCo" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{B95A0533-232D-49B3-80FD-1E659CCB461D}" name="ene" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{4FA9D1B5-12A8-4604-8E31-1378410B4116}" name="feb" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{C949D5DD-B656-4873-AF48-B68220849179}" name="mar" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{0A2BFEA0-7182-4189-B5A7-4FF7AE19A1E3}" name="abr" dataDxfId="65"/>
-    <tableColumn id="6" xr3:uid="{76178BA1-A6FA-4D82-8AFC-D61625038618}" name="may" dataDxfId="64"/>
-    <tableColumn id="7" xr3:uid="{6D8EBE12-BAA6-40B3-9838-8EC0E1D854C0}" name="jun" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{4D6F7AE1-0A4A-4B7D-AD57-EF11C94ED7A7}" name="YTD" dataDxfId="62"/>
+    <tableColumn id="1" xr3:uid="{AC74C680-FF83-44A5-A570-52AEBB5DE765}" name="CeCo" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{B95A0533-232D-49B3-80FD-1E659CCB461D}" name="ene" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{4FA9D1B5-12A8-4604-8E31-1378410B4116}" name="feb" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{C949D5DD-B656-4873-AF48-B68220849179}" name="mar" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{0A2BFEA0-7182-4189-B5A7-4FF7AE19A1E3}" name="abr" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{76178BA1-A6FA-4D82-8AFC-D61625038618}" name="may" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{6D8EBE12-BAA6-40B3-9838-8EC0E1D854C0}" name="jun" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{4D6F7AE1-0A4A-4B7D-AD57-EF11C94ED7A7}" name="YTD" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4FCF9DF4-5C3E-4DA1-B316-5C45F03679A8}" name="Bebida2" displayName="Bebida2" ref="A1:H73" dataDxfId="148">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4FCF9DF4-5C3E-4DA1-B316-5C45F03679A8}" name="Bebida2" displayName="Bebida2" ref="A1:H73" dataDxfId="68">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{BDEC9A2D-F1CB-4191-9A5D-36C157D93B0B}" name="CeCo" dataDxfId="147"/>
-    <tableColumn id="2" xr3:uid="{60D76EA5-57FF-45FB-8457-186785B1E3BC}" name="ene" dataDxfId="146"/>
-    <tableColumn id="3" xr3:uid="{C71CA7B2-ABF3-40D4-8192-DC7E123D2024}" name="feb" dataDxfId="145"/>
-    <tableColumn id="4" xr3:uid="{25F55129-E719-4554-8B64-34CF1D2C669A}" name="mar" dataDxfId="144"/>
-    <tableColumn id="5" xr3:uid="{9B00C926-C150-4C7D-A666-99050F80A8C7}" name="abr" dataDxfId="143"/>
-    <tableColumn id="6" xr3:uid="{D5E4AF0B-39C6-4E12-A4D4-6FCD08001F08}" name="may" dataDxfId="142"/>
-    <tableColumn id="7" xr3:uid="{3618A33C-2533-412F-BC18-6FEB1B9D951D}" name="jun" dataDxfId="141"/>
-    <tableColumn id="8" xr3:uid="{33E35878-7C9B-492D-86FB-31E15D25076E}" name="YTD" dataDxfId="140"/>
+    <tableColumn id="1" xr3:uid="{BDEC9A2D-F1CB-4191-9A5D-36C157D93B0B}" name="CeCo" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{60D76EA5-57FF-45FB-8457-186785B1E3BC}" name="ene" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{C71CA7B2-ABF3-40D4-8192-DC7E123D2024}" name="feb" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{25F55129-E719-4554-8B64-34CF1D2C669A}" name="mar" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{9B00C926-C150-4C7D-A666-99050F80A8C7}" name="abr" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{D5E4AF0B-39C6-4E12-A4D4-6FCD08001F08}" name="may" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{3618A33C-2533-412F-BC18-6FEB1B9D951D}" name="jun" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{33E35878-7C9B-492D-86FB-31E15D25076E}" name="YTD" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3C0EE0A4-4E0D-44E4-A543-91ADD208B26D}" name="Bebida29" displayName="Bebida29" ref="A1:G73" dataDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3C0EE0A4-4E0D-44E4-A543-91ADD208B26D}" name="Bebida29" displayName="Bebida29" ref="A1:G73" dataDxfId="59">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{B00A6E64-852B-457F-871E-16D0189CDAFB}" name="CeCo" dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{E8125C17-9F5F-4C77-8778-C315ECA3BCF6}" name="ene" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{D83DDB2A-976E-4992-8EA5-EF739A3A9A8F}" name="feb" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{3D4BD94F-4ACC-4AE3-A2EF-E27C4B140514}" name="mar" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{60FFDEC4-C645-43DA-A8B8-C573CD6FFA42}" name="abr" dataDxfId="56"/>
-    <tableColumn id="6" xr3:uid="{B87EC187-4AEE-4E3D-8821-FA4796111801}" name="may" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{23BF3F0C-F58B-4688-9370-32CC2F18FA77}" name="jun" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{B00A6E64-852B-457F-871E-16D0189CDAFB}" name="CeCo" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{E8125C17-9F5F-4C77-8778-C315ECA3BCF6}" name="ene" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{D83DDB2A-976E-4992-8EA5-EF739A3A9A8F}" name="feb" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{3D4BD94F-4ACC-4AE3-A2EF-E27C4B140514}" name="mar" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{60FFDEC4-C645-43DA-A8B8-C573CD6FFA42}" name="abr" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{B87EC187-4AEE-4E3D-8821-FA4796111801}" name="may" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{23BF3F0C-F58B-4688-9370-32CC2F18FA77}" name="jun" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2906,87 +2891,87 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}" name="Estabilidad12M" displayName="Estabilidad12M" ref="A1:G73" headerRowDxfId="36" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}" name="Estabilidad12M" displayName="Estabilidad12M" ref="A1:G73" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A1:G73" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8760413A-3DC9-42CF-B4EA-5B5F6E1D9F88}" name="CeCo" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{FD45D0C1-DDDA-4184-B66F-175777AB3E65}" name="ene" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{D2D9EF56-FC3C-407E-B0EE-5525FD2E795B}" name="feb" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{654B09EF-4021-4323-ABAF-B2700F308F33}" name="mar" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{4662FD58-A3D3-406A-BE18-0921110C19A3}" name="abr" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{07656C8D-75E7-44F8-9FEB-C2D1985DD68D}" name="may" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{6C06EEED-C57C-46DE-AB7B-9E9CADAD0F08}" name="jun" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{8760413A-3DC9-42CF-B4EA-5B5F6E1D9F88}" name="CeCo" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{FD45D0C1-DDDA-4184-B66F-175777AB3E65}" name="ene" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{D2D9EF56-FC3C-407E-B0EE-5525FD2E795B}" name="feb" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{654B09EF-4021-4323-ABAF-B2700F308F33}" name="mar" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{4662FD58-A3D3-406A-BE18-0921110C19A3}" name="abr" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{07656C8D-75E7-44F8-9FEB-C2D1985DD68D}" name="may" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{6C06EEED-C57C-46DE-AB7B-9E9CADAD0F08}" name="jun" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{E7B08D3E-9BCB-4339-A04A-AD050E056D06}" name="Estabilidad12M18" displayName="Estabilidad12M18" ref="A1:G73" headerRowDxfId="37" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{E7B08D3E-9BCB-4339-A04A-AD050E056D06}" name="Estabilidad12M18" displayName="Estabilidad12M18" ref="A1:G73" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="A1:G73" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{19B9A2B4-B3D4-44C9-8157-445235E3EEB4}" name="CeCo" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{B1754C82-3B06-4F4F-B512-C855F9CA0A28}" name="ene" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{83379F9C-FAFC-44E2-8B8A-EB49A62B1560}" name="feb" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{C93E3DBE-BD63-4501-960F-EC81078273C5}" name="mar" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{1AEE55EF-1486-4269-AD44-5FCA47F0CA5C}" name="abr" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{E1106030-ECD7-437C-AAD8-98A694A6AFF2}" name="may" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{72B0E4C3-BFAF-4AFC-865A-DA1CBCD78992}" name="jun" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{19B9A2B4-B3D4-44C9-8157-445235E3EEB4}" name="CeCo" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{B1754C82-3B06-4F4F-B512-C855F9CA0A28}" name="ene" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{83379F9C-FAFC-44E2-8B8A-EB49A62B1560}" name="feb" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{C93E3DBE-BD63-4501-960F-EC81078273C5}" name="mar" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{1AEE55EF-1486-4269-AD44-5FCA47F0CA5C}" name="abr" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{E1106030-ECD7-437C-AAD8-98A694A6AFF2}" name="may" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{72B0E4C3-BFAF-4AFC-865A-DA1CBCD78992}" name="jun" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B5A8123F-4602-42B6-83C9-0E8474B2CADF}" name="Barista" displayName="Barista" ref="A1:G73" headerRowDxfId="35" dataDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B5A8123F-4602-42B6-83C9-0E8474B2CADF}" name="Barista" displayName="Barista" ref="A1:G73" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="A1:G73" xr:uid="{B5A8123F-4602-42B6-83C9-0E8474B2CADF}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{7B2B1482-8663-4FFB-8A57-866893B5A61D}" name="CeCo" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{4086DE32-21D4-4E6C-93AB-1F974A9FFBB3}" name="ene" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{E2BB6C81-BE61-4C13-8DE7-683971F67A00}" name="feb" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{B0E78386-D205-4857-A8E3-8F28ECF28F52}" name="mar" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{F809E696-69B4-463B-81DC-21EC1196C761}" name="abr" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{ABFC3013-5DE5-4AF9-BFCB-45FF33E0AC07}" name="may" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{F0E01388-AE42-47AC-87ED-9646838B2E51}" name="jun" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{7B2B1482-8663-4FFB-8A57-866893B5A61D}" name="CeCo" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{4086DE32-21D4-4E6C-93AB-1F974A9FFBB3}" name="ene" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{E2BB6C81-BE61-4C13-8DE7-683971F67A00}" name="feb" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{B0E78386-D205-4857-A8E3-8F28ECF28F52}" name="mar" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{F809E696-69B4-463B-81DC-21EC1196C761}" name="abr" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{ABFC3013-5DE5-4AF9-BFCB-45FF33E0AC07}" name="may" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{F0E01388-AE42-47AC-87ED-9646838B2E51}" name="jun" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{CE1C3205-D3BA-41E4-A414-E8B5D13AFD3D}" name="Supervisor" displayName="Supervisor" ref="A1:G73" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{CE1C3205-D3BA-41E4-A414-E8B5D13AFD3D}" name="Supervisor" displayName="Supervisor" ref="A1:G73" headerRowDxfId="24" dataDxfId="23">
   <autoFilter ref="A1:G73" xr:uid="{CE1C3205-D3BA-41E4-A414-E8B5D13AFD3D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A39D1530-373E-49AC-98C3-67FBDCF66ADF}" name="CeCo" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{05AB85B8-7EE2-4F46-BCB0-D8745A79A727}" name="ene" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{8D184D13-D90E-4C36-927A-4D7F59450943}" name="feb" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{9C9A7828-F85C-41AA-AE6B-C928C791F723}" name="mar" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{858F5C44-74CD-4DDC-B14A-C3C05D1A1230}" name="abr" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{FBE60864-83AB-4532-8B8A-0DE740421BF5}" name="may" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{242FC6BB-64AE-4764-AFEB-2281526B13C4}" name="jun" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{A39D1530-373E-49AC-98C3-67FBDCF66ADF}" name="CeCo" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{05AB85B8-7EE2-4F46-BCB0-D8745A79A727}" name="ene" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{8D184D13-D90E-4C36-927A-4D7F59450943}" name="feb" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{9C9A7828-F85C-41AA-AE6B-C928C791F723}" name="mar" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{858F5C44-74CD-4DDC-B14A-C3C05D1A1230}" name="abr" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{FBE60864-83AB-4532-8B8A-0DE740421BF5}" name="may" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{242FC6BB-64AE-4764-AFEB-2281526B13C4}" name="jun" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{8DE080FC-3BED-4B80-BD7B-7F141035C834}" name="Supervisor22" displayName="Supervisor22" ref="A1:G73" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{8DE080FC-3BED-4B80-BD7B-7F141035C834}" name="Supervisor22" displayName="Supervisor22" ref="A1:G73" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:G73" xr:uid="{8DE080FC-3BED-4B80-BD7B-7F141035C834}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{1A6BE1BB-6BD3-4BAD-9325-F832C6D568A7}" name="CeCo" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{E10BDBC8-E28F-48B7-9653-0911E6C8F18B}" name="ene" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{74E1D7C4-BDDA-4A79-94C9-37C80D43D17A}" name="feb" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{2CB75A52-99BA-4EC4-AAE8-D917C9AB908D}" name="mar" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{7C4B692F-726D-4DFC-95D3-3D55878B9980}" name="abr" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{D16EA3EA-919D-4EBD-98E7-A29DE29F07AC}" name="may" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{43402922-4FFB-465E-B4BE-823EAF456093}" name="jun" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{1A6BE1BB-6BD3-4BAD-9325-F832C6D568A7}" name="CeCo" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{E10BDBC8-E28F-48B7-9653-0911E6C8F18B}" name="ene" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{74E1D7C4-BDDA-4A79-94C9-37C80D43D17A}" name="feb" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{2CB75A52-99BA-4EC4-AAE8-D917C9AB908D}" name="mar" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{7C4B692F-726D-4DFC-95D3-3D55878B9980}" name="abr" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{D16EA3EA-919D-4EBD-98E7-A29DE29F07AC}" name="may" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{43402922-4FFB-465E-B4BE-823EAF456093}" name="jun" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01DC7C7D-B880-4240-925D-62B0CE50CB09}" name="ADTAA" displayName="ADTAA" ref="A1:H69" totalsRowShown="0" headerRowDxfId="139">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01DC7C7D-B880-4240-925D-62B0CE50CB09}" name="ADTAA" displayName="ADTAA" ref="A1:H69" totalsRowShown="0" headerRowDxfId="146">
   <autoFilter ref="A1:H69" xr:uid="{01DC7C7D-B880-4240-925D-62B0CE50CB09}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8FDFBC9A-DC43-478C-9F21-55F0588F95B6}" name="CeCo"/>
@@ -3003,85 +2988,85 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D0C7097E-5E75-45DB-BB3B-3108D178A69C}" name="Tabla3" displayName="Tabla3" ref="A1:H73" totalsRowShown="0" headerRowDxfId="138" dataDxfId="137" tableBorderDxfId="136" dataCellStyle="Porcentaje">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D0C7097E-5E75-45DB-BB3B-3108D178A69C}" name="Tabla3" displayName="Tabla3" ref="A1:H73" totalsRowShown="0" headerRowDxfId="145" dataDxfId="144" tableBorderDxfId="143" dataCellStyle="Porcentaje">
   <autoFilter ref="A1:H73" xr:uid="{D0C7097E-5E75-45DB-BB3B-3108D178A69C}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{C2EFC2B4-3432-4F83-8EA1-D7172138AB9B}" name="CeCo"/>
-    <tableColumn id="2" xr3:uid="{DD1CCE8C-1F33-4D7E-8B7D-850C5836F03D}" name="ene" dataDxfId="135" dataCellStyle="Porcentaje"/>
-    <tableColumn id="3" xr3:uid="{5F81742B-8ACA-4CAA-9BC4-A7EDCFD7AF34}" name="feb" dataDxfId="134" dataCellStyle="Porcentaje"/>
-    <tableColumn id="4" xr3:uid="{CCF6FCAC-A5BC-4B9E-9076-999AC278D7B6}" name="mar" dataDxfId="133" dataCellStyle="Porcentaje"/>
-    <tableColumn id="5" xr3:uid="{54ABFB2E-13EA-427F-91FB-47E666195CF6}" name="abr" dataDxfId="132" dataCellStyle="Porcentaje"/>
-    <tableColumn id="6" xr3:uid="{22800C96-3B11-4883-80D9-26FEA549F2EF}" name="may" dataDxfId="131" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{9AE01694-9EB4-4C3E-8091-31272AA10FAC}" name="jun" dataDxfId="130" dataCellStyle="Porcentaje"/>
-    <tableColumn id="9" xr3:uid="{9AEE286D-E013-445D-8F31-2EDBF809F4EE}" name="YTD" dataDxfId="129" dataCellStyle="Porcentaje"/>
+    <tableColumn id="2" xr3:uid="{DD1CCE8C-1F33-4D7E-8B7D-850C5836F03D}" name="ene" dataDxfId="142" dataCellStyle="Porcentaje"/>
+    <tableColumn id="3" xr3:uid="{5F81742B-8ACA-4CAA-9BC4-A7EDCFD7AF34}" name="feb" dataDxfId="141" dataCellStyle="Porcentaje"/>
+    <tableColumn id="4" xr3:uid="{CCF6FCAC-A5BC-4B9E-9076-999AC278D7B6}" name="mar" dataDxfId="140" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{54ABFB2E-13EA-427F-91FB-47E666195CF6}" name="abr" dataDxfId="139" dataCellStyle="Porcentaje"/>
+    <tableColumn id="6" xr3:uid="{22800C96-3B11-4883-80D9-26FEA549F2EF}" name="may" dataDxfId="138" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{9AE01694-9EB4-4C3E-8091-31272AA10FAC}" name="jun" dataDxfId="137" dataCellStyle="Porcentaje"/>
+    <tableColumn id="9" xr3:uid="{9AEE286D-E013-445D-8F31-2EDBF809F4EE}" name="YTD" dataDxfId="136" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AF4AFD2D-F1F3-4FAB-BCF9-9DC13F7DF0DB}" name="vsppto" displayName="vsppto" ref="A1:H73" totalsRowShown="0" headerRowDxfId="128" tableBorderDxfId="127">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AF4AFD2D-F1F3-4FAB-BCF9-9DC13F7DF0DB}" name="vsppto" displayName="vsppto" ref="A1:H73" totalsRowShown="0" headerRowDxfId="135" tableBorderDxfId="134">
   <autoFilter ref="A1:H73" xr:uid="{AF4AFD2D-F1F3-4FAB-BCF9-9DC13F7DF0DB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1B86AC11-BA6E-4409-9BCC-D0BFC1CD56F4}" name="CeCo" dataDxfId="126"/>
-    <tableColumn id="2" xr3:uid="{0F192631-4FFF-4FD5-A95D-3C108F8BE19E}" name="ene" dataDxfId="125"/>
-    <tableColumn id="3" xr3:uid="{6C8B16E6-4F77-41EA-8B61-4534855E870F}" name="feb" dataDxfId="124"/>
-    <tableColumn id="4" xr3:uid="{94D35D35-5DDF-4D12-805B-731F38DE0744}" name="mar" dataDxfId="123"/>
-    <tableColumn id="5" xr3:uid="{3440F7B1-3F7A-4549-9C3E-B7C6B54E89C3}" name="abr" dataDxfId="122"/>
-    <tableColumn id="6" xr3:uid="{6FEDA900-B0EC-4A56-A276-007F8F32C55D}" name="may" dataDxfId="121"/>
-    <tableColumn id="7" xr3:uid="{81D19149-D98D-4166-BE81-99492658343E}" name="jun" dataDxfId="120"/>
-    <tableColumn id="9" xr3:uid="{FC882C39-EC0B-4DDB-AA25-5A67064B8F8F}" name="YTD" dataDxfId="119"/>
+    <tableColumn id="1" xr3:uid="{1B86AC11-BA6E-4409-9BCC-D0BFC1CD56F4}" name="CeCo" dataDxfId="133"/>
+    <tableColumn id="2" xr3:uid="{0F192631-4FFF-4FD5-A95D-3C108F8BE19E}" name="ene" dataDxfId="132"/>
+    <tableColumn id="3" xr3:uid="{6C8B16E6-4F77-41EA-8B61-4534855E870F}" name="feb" dataDxfId="131"/>
+    <tableColumn id="4" xr3:uid="{94D35D35-5DDF-4D12-805B-731F38DE0744}" name="mar" dataDxfId="130"/>
+    <tableColumn id="5" xr3:uid="{3440F7B1-3F7A-4549-9C3E-B7C6B54E89C3}" name="abr" dataDxfId="129"/>
+    <tableColumn id="6" xr3:uid="{6FEDA900-B0EC-4A56-A276-007F8F32C55D}" name="may" dataDxfId="128"/>
+    <tableColumn id="7" xr3:uid="{81D19149-D98D-4166-BE81-99492658343E}" name="jun" dataDxfId="127"/>
+    <tableColumn id="9" xr3:uid="{FC882C39-EC0B-4DDB-AA25-5A67064B8F8F}" name="YTD" dataDxfId="126"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{785FD011-3A39-431D-A263-BADB6BDE3D94}" name="ATAA" displayName="ATAA" ref="A1:H73" totalsRowShown="0" headerRowDxfId="118" tableBorderDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{785FD011-3A39-431D-A263-BADB6BDE3D94}" name="ATAA" displayName="ATAA" ref="A1:H73" totalsRowShown="0" headerRowDxfId="125" tableBorderDxfId="124">
   <autoFilter ref="A1:H73" xr:uid="{AF4AFD2D-F1F3-4FAB-BCF9-9DC13F7DF0DB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{59F38E1E-38B2-46EB-AA01-ADB6B981128B}" name="CeCo" dataDxfId="116"/>
-    <tableColumn id="2" xr3:uid="{649F4E8B-772D-4A07-883A-297BE711DD85}" name="ene" dataDxfId="115"/>
-    <tableColumn id="3" xr3:uid="{66FA2D07-7D7A-4218-A261-1BD7FC710740}" name="feb" dataDxfId="114"/>
-    <tableColumn id="4" xr3:uid="{211538EC-1884-443F-8454-BA77B7F28EB8}" name="mar" dataDxfId="113"/>
-    <tableColumn id="5" xr3:uid="{5FAA8758-FD12-4BE9-8965-A65E5A65313A}" name="abr" dataDxfId="112"/>
-    <tableColumn id="6" xr3:uid="{7A0AFBD2-AD5B-4447-9BE2-1EFC4F9F14E6}" name="may" dataDxfId="111"/>
-    <tableColumn id="7" xr3:uid="{2E6A7F3C-986D-45C2-8461-88E38A95D878}" name="jun" dataDxfId="110"/>
-    <tableColumn id="9" xr3:uid="{C4817951-A012-4EB9-A097-61BDB11840CF}" name="YTD" dataDxfId="109"/>
+    <tableColumn id="1" xr3:uid="{59F38E1E-38B2-46EB-AA01-ADB6B981128B}" name="CeCo" dataDxfId="123"/>
+    <tableColumn id="2" xr3:uid="{649F4E8B-772D-4A07-883A-297BE711DD85}" name="ene" dataDxfId="122"/>
+    <tableColumn id="3" xr3:uid="{66FA2D07-7D7A-4218-A261-1BD7FC710740}" name="feb" dataDxfId="121"/>
+    <tableColumn id="4" xr3:uid="{211538EC-1884-443F-8454-BA77B7F28EB8}" name="mar" dataDxfId="120"/>
+    <tableColumn id="5" xr3:uid="{5FAA8758-FD12-4BE9-8965-A65E5A65313A}" name="abr" dataDxfId="119"/>
+    <tableColumn id="6" xr3:uid="{7A0AFBD2-AD5B-4447-9BE2-1EFC4F9F14E6}" name="may" dataDxfId="118"/>
+    <tableColumn id="7" xr3:uid="{2E6A7F3C-986D-45C2-8461-88E38A95D878}" name="jun" dataDxfId="117"/>
+    <tableColumn id="9" xr3:uid="{C4817951-A012-4EB9-A097-61BDB11840CF}" name="YTD" dataDxfId="116"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2DD3D2A3-A6E2-4CB5-9D8E-24B27DF07237}" name="COGs" displayName="COGs" ref="A1:H73" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107" tableBorderDxfId="106" dataCellStyle="Porcentaje">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2DD3D2A3-A6E2-4CB5-9D8E-24B27DF07237}" name="COGs" displayName="COGs" ref="A1:H73" totalsRowShown="0" headerRowDxfId="115" dataDxfId="114" tableBorderDxfId="113" dataCellStyle="Porcentaje">
   <autoFilter ref="A1:H73" xr:uid="{2DD3D2A3-A6E2-4CB5-9D8E-24B27DF07237}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{667DC932-8C9B-46B6-B69B-96B71DAF4178}" name="CeCo"/>
-    <tableColumn id="2" xr3:uid="{25813112-0CE9-407E-96F8-B767A9AE96A5}" name="ene" dataDxfId="105" dataCellStyle="Porcentaje"/>
-    <tableColumn id="3" xr3:uid="{E3C2F824-C740-4FC7-9642-451285CB6F5D}" name="feb" dataDxfId="104" dataCellStyle="Porcentaje"/>
-    <tableColumn id="4" xr3:uid="{7DBF1ADB-188E-4719-B609-90E4FAE2B065}" name="mar" dataDxfId="103" dataCellStyle="Porcentaje"/>
-    <tableColumn id="5" xr3:uid="{64D0EC7E-5580-47D9-9282-8484D3456183}" name="abr" dataDxfId="102" dataCellStyle="Porcentaje"/>
-    <tableColumn id="6" xr3:uid="{D79D7ABE-ED71-4183-A66E-79E1CC6B60FA}" name="may" dataDxfId="101" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{17FCC6E9-A5AD-4020-A99D-814FE44E7F5D}" name="jun" dataDxfId="100" dataCellStyle="Porcentaje"/>
-    <tableColumn id="8" xr3:uid="{3222E955-FFE4-46F7-B236-F5CA3C55ED76}" name="YTD" dataDxfId="99" dataCellStyle="Porcentaje"/>
+    <tableColumn id="2" xr3:uid="{25813112-0CE9-407E-96F8-B767A9AE96A5}" name="ene" dataDxfId="112" dataCellStyle="Porcentaje"/>
+    <tableColumn id="3" xr3:uid="{E3C2F824-C740-4FC7-9642-451285CB6F5D}" name="feb" dataDxfId="111" dataCellStyle="Porcentaje"/>
+    <tableColumn id="4" xr3:uid="{7DBF1ADB-188E-4719-B609-90E4FAE2B065}" name="mar" dataDxfId="110" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{64D0EC7E-5580-47D9-9282-8484D3456183}" name="abr" dataDxfId="109" dataCellStyle="Porcentaje"/>
+    <tableColumn id="6" xr3:uid="{D79D7ABE-ED71-4183-A66E-79E1CC6B60FA}" name="may" dataDxfId="108" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{17FCC6E9-A5AD-4020-A99D-814FE44E7F5D}" name="jun" dataDxfId="107" dataCellStyle="Porcentaje"/>
+    <tableColumn id="8" xr3:uid="{3222E955-FFE4-46F7-B236-F5CA3C55ED76}" name="YTD" dataDxfId="106" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{26E4F941-1AF1-4001-AEDB-7D7F50D6DF3C}" name="Tabla7" displayName="Tabla7" ref="A1:H73" totalsRowShown="0" headerRowDxfId="98" dataDxfId="97" tableBorderDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{26E4F941-1AF1-4001-AEDB-7D7F50D6DF3C}" name="Tabla7" displayName="Tabla7" ref="A1:H73" totalsRowShown="0" headerRowDxfId="105" dataDxfId="104" tableBorderDxfId="103">
   <autoFilter ref="A1:H73" xr:uid="{26E4F941-1AF1-4001-AEDB-7D7F50D6DF3C}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{45603471-A800-4D4D-B27B-793376C68BE7}" name="CeCo"/>
-    <tableColumn id="2" xr3:uid="{FF41D456-26E8-4A96-85C1-0DE38E3AB2F8}" name="ene" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{554B0815-E0AE-45F8-926D-06F26DE3B057}" name="feb" dataDxfId="94"/>
-    <tableColumn id="4" xr3:uid="{736CBF7F-B990-42E7-B15E-5B0C67E537EE}" name="mar" dataDxfId="93"/>
-    <tableColumn id="5" xr3:uid="{A234C2C3-97E3-4872-A2DE-111C792DC591}" name="abr" dataDxfId="92"/>
-    <tableColumn id="6" xr3:uid="{791C4ED2-A9F3-4442-900E-D66577C955BF}" name="may" dataDxfId="91"/>
-    <tableColumn id="7" xr3:uid="{696D958C-1D64-4C51-AE13-F3BBC6A497F1}" name="jun" dataDxfId="90"/>
-    <tableColumn id="8" xr3:uid="{8D86F959-E75E-48A9-B708-E9580836BAB6}" name="YTD" dataDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{FF41D456-26E8-4A96-85C1-0DE38E3AB2F8}" name="ene" dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{554B0815-E0AE-45F8-926D-06F26DE3B057}" name="feb" dataDxfId="101"/>
+    <tableColumn id="4" xr3:uid="{736CBF7F-B990-42E7-B15E-5B0C67E537EE}" name="mar" dataDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{A234C2C3-97E3-4872-A2DE-111C792DC591}" name="abr" dataDxfId="99"/>
+    <tableColumn id="6" xr3:uid="{791C4ED2-A9F3-4442-900E-D66577C955BF}" name="may" dataDxfId="98"/>
+    <tableColumn id="7" xr3:uid="{696D958C-1D64-4C51-AE13-F3BBC6A497F1}" name="jun" dataDxfId="97"/>
+    <tableColumn id="8" xr3:uid="{8D86F959-E75E-48A9-B708-E9580836BAB6}" name="YTD" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3104,16 +3089,16 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{FF52C812-65CA-4F77-A20D-9577DD80438C}" name="Conexion" displayName="Conexion" ref="A1:H73" dataDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{FF52C812-65CA-4F77-A20D-9577DD80438C}" name="Conexion" displayName="Conexion" ref="A1:H73" dataDxfId="95">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{CBEFF17C-36D0-4285-B054-C2717E2F836E}" name="CeCo" dataDxfId="87"/>
-    <tableColumn id="2" xr3:uid="{723CF5E2-1296-4829-B678-30B9F1C59839}" name="ene" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{AEF08694-1B5C-472F-9138-C35C6046EF1E}" name="feb" dataDxfId="85"/>
-    <tableColumn id="4" xr3:uid="{C8B61DB1-6698-4C99-8019-D7366922E31C}" name="mar" dataDxfId="84"/>
-    <tableColumn id="5" xr3:uid="{AA297A15-CBAC-4D29-8354-6E845D1FE939}" name="abr" dataDxfId="83"/>
-    <tableColumn id="6" xr3:uid="{EADFFD7F-EF42-42E2-889B-295973B77A72}" name="may" dataDxfId="82"/>
-    <tableColumn id="7" xr3:uid="{955A7129-B6F6-47A2-AD6F-CA12B3E0592A}" name="jun" dataDxfId="81"/>
-    <tableColumn id="8" xr3:uid="{554452BD-6543-4D8C-88F4-78E82C298799}" name="YTD" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{CBEFF17C-36D0-4285-B054-C2717E2F836E}" name="CeCo" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{723CF5E2-1296-4829-B678-30B9F1C59839}" name="ene" dataDxfId="93"/>
+    <tableColumn id="3" xr3:uid="{AEF08694-1B5C-472F-9138-C35C6046EF1E}" name="feb" dataDxfId="92"/>
+    <tableColumn id="4" xr3:uid="{C8B61DB1-6698-4C99-8019-D7366922E31C}" name="mar" dataDxfId="91"/>
+    <tableColumn id="5" xr3:uid="{AA297A15-CBAC-4D29-8354-6E845D1FE939}" name="abr" dataDxfId="90"/>
+    <tableColumn id="6" xr3:uid="{EADFFD7F-EF42-42E2-889B-295973B77A72}" name="may" dataDxfId="89"/>
+    <tableColumn id="7" xr3:uid="{955A7129-B6F6-47A2-AD6F-CA12B3E0592A}" name="jun" dataDxfId="88"/>
+    <tableColumn id="8" xr3:uid="{554452BD-6543-4D8C-88F4-78E82C298799}" name="YTD" dataDxfId="87"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3448,47 +3433,47 @@
     <col min="13" max="13" width="8.6328125" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="6.81640625" bestFit="1" customWidth="1"/>
     <col min="16" max="20" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="29" customHeight="1">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="41" t="s">
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="41" t="s">
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="44" t="s">
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="40" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="2" spans="2:22">
-      <c r="B2" s="46"/>
-      <c r="C2" s="45"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="29" t="s">
         <v>109</v>
       </c>
@@ -3543,21 +3528,21 @@
       <c r="U2" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="V2" s="44"/>
+      <c r="V2" s="40"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="V3" s="47">
+      <c r="V3" s="35">
         <v>0.88</v>
       </c>
     </row>
     <row r="4" spans="2:22">
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="36" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -3565,7 +3550,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="36" t="s">
         <v>13</v>
       </c>
       <c r="C5">
@@ -3573,7 +3558,7 @@
       </c>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="36" t="s">
         <v>14</v>
       </c>
       <c r="C6">
@@ -3582,12 +3567,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:J1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23514,7 +23499,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="32" t="s">
         <v>94</v>
       </c>
       <c r="B8" t="s">
@@ -23599,7 +23584,7 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="35" t="s">
+      <c r="A13" t="s">
         <v>108</v>
       </c>
       <c r="B13" t="s">
@@ -23616,7 +23601,7 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="37" t="s">
+      <c r="A14" t="s">
         <v>98</v>
       </c>
       <c r="B14" t="s">
@@ -23633,7 +23618,7 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="37" t="s">
+      <c r="A15" t="s">
         <v>98</v>
       </c>
       <c r="B15" t="s">
@@ -23650,7 +23635,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="37" t="s">
+      <c r="A16" t="s">
         <v>98</v>
       </c>
       <c r="B16" t="s">
@@ -23667,7 +23652,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="37" t="s">
+      <c r="A17" t="s">
         <v>98</v>
       </c>
       <c r="B17" t="s">
@@ -23684,7 +23669,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="37" t="s">
+      <c r="A18" t="s">
         <v>98</v>
       </c>
       <c r="B18" t="s">
@@ -23701,7 +23686,7 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="37" t="s">
+      <c r="A19" t="s">
         <v>98</v>
       </c>
       <c r="B19" t="s">
